--- a/tame_output/ON/bt/strategyON_20240128.xlsx
+++ b/tame_output/ON/bt/strategyON_20240128.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-01-26</t>
+          <t>2024-01-27</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>1.1%</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-01-26</t>
+          <t>2024-01-27</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>2.4%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -931,11 +931,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-01-26</t>
+          <t>2024-01-27</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-20.1%</t>
+          <t>-20.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>101.2%</t>
+          <t>101.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-01-26</t>
+          <t>2024-01-27</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>3.8%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,16 +1242,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-01-26</t>
+          <t>2024-01-27</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.8%</t>
+          <t>-155.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>2.5%</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-01-26</t>
+          <t>2024-01-27</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>3.9%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1855"/>
+  <dimension ref="A1:G1856"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278796973926473</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44226,6 +44226,29 @@
       </c>
       <c r="G1855" t="n">
         <v>4.497547831119687</v>
+      </c>
+    </row>
+    <row r="1856">
+      <c r="A1856" s="2" t="n">
+        <v>45318</v>
+      </c>
+      <c r="B1856" t="n">
+        <v>3.291648619981434</v>
+      </c>
+      <c r="C1856" t="n">
+        <v>3.139859661206862</v>
+      </c>
+      <c r="D1856" t="n">
+        <v>1.650728355763547</v>
+      </c>
+      <c r="E1856" t="n">
+        <v>3.799794579198533</v>
+      </c>
+      <c r="F1856" t="n">
+        <v>2.26480790435053</v>
+      </c>
+      <c r="G1856" t="n">
+        <v>4.49874440381718</v>
       </c>
     </row>
   </sheetData>
